--- a/backend/data/attachments/risk_风险事件应急预案_9.xlsx
+++ b/backend/data/attachments/risk_风险事件应急预案_9.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trust-984</t>
+          <t>Trust-734</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9575</v>
+        <v>41792</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -464,28 +464,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trust-940</t>
+          <t>Trust-817</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5168</v>
+        <v>24804</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,28 +494,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trust-986</t>
+          <t>Trust-411</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14738</v>
+        <v>37284</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -524,42 +524,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trust-566</t>
+          <t>Trust-497</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26088</v>
+        <v>34729</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,11 +571,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trust-976</t>
+          <t>Trust-524</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31920</v>
+        <v>47920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -584,28 +584,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trust-495</t>
+          <t>Trust-133</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48495</v>
+        <v>29283</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,11 +631,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trust-990</t>
+          <t>Trust-201</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11577</v>
+        <v>49936</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -644,12 +644,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -661,11 +661,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trust-839</t>
+          <t>Trust-294</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14447</v>
+        <v>13005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -674,12 +674,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
